--- a/artfynd/A 9939-2026 artfynd.xlsx
+++ b/artfynd/A 9939-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122127666</v>
+        <v>122127651</v>
       </c>
       <c r="B2" t="n">
-        <v>57753</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,16 +703,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>hane</t>
@@ -734,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437247</v>
+        <v>437258</v>
       </c>
       <c r="R2" t="n">
-        <v>6243172</v>
+        <v>6243246</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,12 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122127651</v>
+        <v>122127666</v>
       </c>
       <c r="B3" t="n">
-        <v>57753</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,7 +814,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>hane</t>
@@ -850,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437258</v>
+        <v>437247</v>
       </c>
       <c r="R3" t="n">
-        <v>6243246</v>
+        <v>6243172</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,12 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,6 +899,352 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>FNT0019 Osby Östra Genastorp häckfågelinventering 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122127843</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Östra Genastorp, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>437323</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6243250</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Julia Björk</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>FNT0019 Osby Östra Genastorp häckfågelinventering 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122127836</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Östra Genastorp, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>437199</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6243243</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Julia Björk</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>FNT0019 Osby Östra Genastorp häckfågelinventering 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122127647</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Östra Genastorp, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>437300</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6243224</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Julia Björk</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>FNT0019 Osby Östra Genastorp häckfågelinventering 2024</t>
         </is>
